--- a/outputs/reports/catboost/feature_importance_top10.xlsx
+++ b/outputs/reports/catboost/feature_importance_top10.xlsx
@@ -470,19 +470,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FTEP_STF_NUM</t>
+          <t>DEPT_CD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>상근직원수</t>
+          <t>부서코드</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.07476412271520354</v>
+        <v>0.06671461789117154</v>
       </c>
       <c r="F2" t="n">
-        <v>7.476412271520343</v>
+        <v>6.671461789117155</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=7.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -515,10 +515,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.06525520175242064</v>
+        <v>0.06495441989195058</v>
       </c>
       <c r="F3" t="n">
-        <v>6.525520175242055</v>
+        <v>6.495441989195059</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.53%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자시도코드(AID_BZR_CAP_CD). 기여도(정규화 비중)=6.50%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -542,19 +542,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DEPT_CD</t>
+          <t>INST_TY_CD</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>부서코드</t>
+          <t>기관유형코드</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.06142095487706396</v>
+        <v>0.05547755973096497</v>
       </c>
       <c r="F4" t="n">
-        <v>6.142095487706388</v>
+        <v>5.547755973096498</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>변수 의미: 부서코드(DEPT_CD). 기여도(정규화 비중)=6.14%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 기관유형코드(INST_TY_CD). 기여도(정규화 비중)=5.55%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -578,19 +578,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RPRSV_AGGP_DV_CD</t>
+          <t>AID_BZR_FNDN_YS</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>대표자연령대구분코드</t>
+          <t>보조사업자설립년수</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.04453851651510576</v>
+        <v>0.05417814811546744</v>
       </c>
       <c r="F5" t="n">
-        <v>4.453851651510569</v>
+        <v>5.417814811546745</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -599,7 +599,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=4.45%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=5.42%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -614,19 +614,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SECT_CD</t>
+          <t>RPRSV_AGGP_DV_CD</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>부문코드</t>
+          <t>대표자연령대구분코드</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.04184806361799587</v>
+        <v>0.05058522443296955</v>
       </c>
       <c r="F6" t="n">
-        <v>4.184806361799581</v>
+        <v>5.058522443296956</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=4.18%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자연령대구분코드(RPRSV_AGGP_DV_CD). 기여도(정규화 비중)=5.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -650,19 +650,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AID_BZR_FNDN_YS</t>
+          <t>FTEP_STF_NUM</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>보조사업자설립년수</t>
+          <t>상근직원수</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.03966638691246891</v>
+        <v>0.04458071949171321</v>
       </c>
       <c r="F7" t="n">
-        <v>3.966638691246886</v>
+        <v>4.458071949171321</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>변수 의미: 보조사업자설립년수(AID_BZR_FNDN_YS). 기여도(정규화 비중)=3.97%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 상근직원수(FTEP_STF_NUM). 기여도(정규화 비중)=4.46%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -686,19 +686,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LAF_CD</t>
+          <t>RPRSV_HSHD_DV_CD</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>지방자치단체코드</t>
+          <t>대표자세대구분코드</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.03890392119087331</v>
+        <v>0.04060187085898578</v>
       </c>
       <c r="F8" t="n">
-        <v>3.890392119087326</v>
+        <v>4.060187085898579</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -707,7 +707,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.89%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 대표자세대구분코드(RPRSV_HSHD_DV_CD). 기여도(정규화 비중)=4.06%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -722,19 +722,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BIZCT_SUM_AMT</t>
+          <t>LAF_CD</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>사업비합계금액</t>
+          <t>지방자치단체코드</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.03803318886386643</v>
+        <v>0.03611816776722611</v>
       </c>
       <c r="F9" t="n">
-        <v>3.803318886386638</v>
+        <v>3.611816776722611</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>변수 의미: 사업비합계금액(BIZCT_SUM_AMT). 기여도(정규화 비중)=3.80%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 지방자치단체코드(LAF_CD). 기여도(정규화 비중)=3.61%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -758,19 +758,19 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RPRSV_DSCRD_YN</t>
+          <t>SECT_CD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>대표자불일치여부</t>
+          <t>부문코드</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.03769171190310019</v>
+        <v>0.03477271178468273</v>
       </c>
       <c r="F10" t="n">
-        <v>3.769171190310014</v>
+        <v>3.477271178468274</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>변수 의미: 대표자불일치여부(RPRSV_DSCRD_YN). 기여도(정규화 비중)=3.77%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 부문코드(SECT_CD). 기여도(정규화 비중)=3.48%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
@@ -794,19 +794,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>THY_PFM_AID_BIZ_NUM</t>
+          <t>LBST_PLAN_RT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>당해년도수행보조사업수</t>
+          <t>인건비계획비율</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.03669786363562316</v>
+        <v>0.0344039068366</v>
       </c>
       <c r="F11" t="n">
-        <v>3.669786363562311</v>
+        <v>3.44039068366</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -815,7 +815,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>변수 의미: 당해년도수행보조사업수(THY_PFM_AID_BIZ_NUM). 기여도(정규화 비중)=3.67%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
+          <t>변수 의미: 인건비계획비율(LBST_PLAN_RT). 기여도(정규화 비중)=3.44%. 측정방법: CatBoost 예측값 변화에 대한 기여도(PredictionValuesChange)입니다. 값이 클수록 위험도 점수에 미치는 영향이 큽니다.</t>
         </is>
       </c>
     </row>
